--- a/frontend/public/ejemplos/ppe_propiedad_planta/RQ-001_activos.xlsx
+++ b/frontend/public/ejemplos/ppe_propiedad_planta/RQ-001_activos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Léame" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Datos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Instrucciones" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,16 +26,60 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F6B4C"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="006B7280"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F6B4C"/>
+    </font>
+    <font>
+      <color rgb="006B7280"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F6B4C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="006B7280"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F1EC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -43,12 +87,46 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D1D5DB"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D1D5DB"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D1D5DB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D1D5DB"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -416,688 +494,710 @@
   </sheetPr>
   <dimension ref="A1:T11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="29" customWidth="1" min="5" max="5"/>
+    <col width="27" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="34" customWidth="1" min="12" max="12"/>
+    <col width="23" customWidth="1" min="13" max="13"/>
+    <col width="23" customWidth="1" min="14" max="14"/>
+    <col width="28" customWidth="1" min="15" max="15"/>
+    <col width="34" customWidth="1" min="16" max="16"/>
+    <col width="34" customWidth="1" min="17" max="17"/>
+    <col width="17" customWidth="1" min="18" max="18"/>
+    <col width="23" customWidth="1" min="19" max="19"/>
+    <col width="34" customWidth="1" min="20" max="20"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Código del activo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Descripción</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Clase</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Elemento al que pertenece (componente)</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Fecha disponible para uso</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Costo al inicio del año</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Adiciones del año</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Valor residual</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>Vida útil (meses)</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>Método de depreciación</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>Depreciación acumulada inicial</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>Depreciación del año registrada</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>Deterioro acumulado</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>Importe recuperable</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>Valor revaluado al corte</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>Superávit de revaluación previo</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>Decremento previo del mismo activo reconocido en resultados</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t>Fecha de baja</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="2" t="inlineStr">
         <is>
           <t>Producto de la baja</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="2" t="inlineStr">
         <is>
           <t>Ganancia (pérdida) registrada en la baja</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>EDIF-01</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Edificio administrativo</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Edificios</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr"/>
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>01/01/2015</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>500000</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr"/>
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>50000</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>480</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>Lineal</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>112500</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr">
         <is>
           <t>11250</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
+      <c r="M2" s="3" t="inlineStr"/>
+      <c r="N2" s="3" t="inlineStr"/>
+      <c r="O2" s="3" t="inlineStr"/>
+      <c r="P2" s="3" t="inlineStr"/>
+      <c r="Q2" s="3" t="inlineStr"/>
+      <c r="R2" s="3" t="inlineStr"/>
+      <c r="S2" s="3" t="inlineStr"/>
+      <c r="T2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>TERR-01</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>Terreno planta</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>Terrenos</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr"/>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>01/01/2015</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>300000</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr"/>
+      <c r="I3" s="4" t="inlineStr"/>
+      <c r="J3" s="4" t="inlineStr"/>
+      <c r="K3" s="4" t="inlineStr"/>
+      <c r="L3" s="4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr">
+      <c r="M3" s="4" t="inlineStr"/>
+      <c r="N3" s="4" t="inlineStr"/>
+      <c r="O3" s="4" t="inlineStr">
         <is>
           <t>360000</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
+      <c r="P3" s="4" t="inlineStr"/>
+      <c r="Q3" s="4" t="inlineStr"/>
+      <c r="R3" s="4" t="inlineStr"/>
+      <c r="S3" s="4" t="inlineStr"/>
+      <c r="T3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>TERR-02</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Terreno bodega</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Terrenos</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr"/>
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>01/05/2018</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>80000</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr"/>
+      <c r="I4" s="3" t="inlineStr"/>
+      <c r="J4" s="3" t="inlineStr"/>
+      <c r="K4" s="3" t="inlineStr"/>
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
+      <c r="M4" s="3" t="inlineStr"/>
+      <c r="N4" s="3" t="inlineStr"/>
+      <c r="O4" s="3" t="inlineStr"/>
+      <c r="P4" s="3" t="inlineStr"/>
+      <c r="Q4" s="3" t="inlineStr"/>
+      <c r="R4" s="3" t="inlineStr"/>
+      <c r="S4" s="3" t="inlineStr"/>
+      <c r="T4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>VEH-01</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Camioneta 4x4</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>Vehículos</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr"/>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>01/07/2023</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>40000</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>4000</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>Lineal</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K5" s="4" t="inlineStr">
         <is>
           <t>10800</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L5" s="4" t="inlineStr">
         <is>
           <t>6000</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
+      <c r="M5" s="4" t="inlineStr"/>
+      <c r="N5" s="4" t="inlineStr"/>
+      <c r="O5" s="4" t="inlineStr"/>
+      <c r="P5" s="4" t="inlineStr"/>
+      <c r="Q5" s="4" t="inlineStr"/>
+      <c r="R5" s="4" t="inlineStr"/>
+      <c r="S5" s="4" t="inlineStr"/>
+      <c r="T5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>VEH-02</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Camión de reparto</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Vehículos</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr"/>
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>01/01/2021</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>30000</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>Lineal</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K6" s="3" t="inlineStr">
         <is>
           <t>21600</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L6" s="3" t="inlineStr">
         <is>
           <t>2700</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr">
+      <c r="M6" s="3" t="inlineStr"/>
+      <c r="N6" s="3" t="inlineStr"/>
+      <c r="O6" s="3" t="inlineStr"/>
+      <c r="P6" s="3" t="inlineStr"/>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr">
         <is>
           <t>30/06/2025</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S6" s="3" t="inlineStr">
         <is>
           <t>9000</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T6" s="3" t="inlineStr">
         <is>
           <t>1500</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>MAQ-01</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Línea de envasado</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>Maquinaria</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr"/>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>01/01/2020</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>120000</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr"/>
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>120</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J7" s="4" t="inlineStr">
         <is>
           <t>Lineal</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K7" s="4" t="inlineStr">
         <is>
           <t>60000</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="L7" s="4" t="inlineStr">
         <is>
           <t>12000</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
+      <c r="M7" s="4" t="inlineStr"/>
+      <c r="N7" s="4" t="inlineStr">
         <is>
           <t>40000</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
+      <c r="O7" s="4" t="inlineStr"/>
+      <c r="P7" s="4" t="inlineStr"/>
+      <c r="Q7" s="4" t="inlineStr"/>
+      <c r="R7" s="4" t="inlineStr"/>
+      <c r="S7" s="4" t="inlineStr"/>
+      <c r="T7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>MAQ-01-M</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Motor de la línea de envasado</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Maquinaria</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>MAQ-01</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>01/01/2020</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>30000</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr"/>
+      <c r="I8" s="3" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>Lineal</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K8" s="3" t="inlineStr">
         <is>
           <t>30000</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="L8" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
+      <c r="M8" s="3" t="inlineStr"/>
+      <c r="N8" s="3" t="inlineStr"/>
+      <c r="O8" s="3" t="inlineStr"/>
+      <c r="P8" s="3" t="inlineStr"/>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr"/>
+      <c r="S8" s="3" t="inlineStr"/>
+      <c r="T8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>EQC-01</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Servidores</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>Equipo de cómputo</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr"/>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>01/01/2024</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>15000</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr"/>
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J9" s="4" t="inlineStr">
         <is>
           <t>Unidades producidas</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K9" s="4" t="inlineStr">
         <is>
           <t>5000</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="L9" s="4" t="inlineStr">
         <is>
           <t>4000</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
+      <c r="M9" s="4" t="inlineStr"/>
+      <c r="N9" s="4" t="inlineStr"/>
+      <c r="O9" s="4" t="inlineStr"/>
+      <c r="P9" s="4" t="inlineStr"/>
+      <c r="Q9" s="4" t="inlineStr"/>
+      <c r="R9" s="4" t="inlineStr"/>
+      <c r="S9" s="4" t="inlineStr"/>
+      <c r="T9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>OBRA-01</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Nave industrial en construcción</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>Construcciones en curso</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr"/>
+      <c r="E10" s="3" t="inlineStr"/>
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr"/>
+      <c r="I10" s="3" t="inlineStr"/>
+      <c r="J10" s="3" t="inlineStr"/>
+      <c r="K10" s="3" t="inlineStr"/>
+      <c r="L10" s="3" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
+      <c r="M10" s="3" t="inlineStr"/>
+      <c r="N10" s="3" t="inlineStr"/>
+      <c r="O10" s="3" t="inlineStr"/>
+      <c r="P10" s="3" t="inlineStr"/>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr"/>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>MOB-01</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Mobiliario de oficinas</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>Muebles y enseres</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr"/>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>01/04/2025</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>12000</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr"/>
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>120</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J11" s="4" t="inlineStr">
         <is>
           <t>Lineal</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
+      <c r="K11" s="4" t="inlineStr"/>
+      <c r="L11" s="4" t="inlineStr">
         <is>
           <t>904.11</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
+      <c r="M11" s="4" t="inlineStr"/>
+      <c r="N11" s="4" t="inlineStr"/>
+      <c r="O11" s="4" t="inlineStr"/>
+      <c r="P11" s="4" t="inlineStr"/>
+      <c r="Q11" s="4" t="inlineStr"/>
+      <c r="R11" s="4" t="inlineStr"/>
+      <c r="S11" s="4" t="inlineStr"/>
+      <c r="T11" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1110,36 +1210,325 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>AuditConsulting Auditores Cía. Ltda.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Auxiliar de propiedad, planta y equipo por activo al corte</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Una fila por activo o componente: código, descripción, clase, elemento (si es parte), fecha disponible para uso, costo inicial, adiciones, residual, vida útil en meses, método, depreciación acumulada inicial, depreciación del año registrada, deterioro acumulado; si aplica: importe recuperable, valor revaluado, superávit previo, fecha y producto de la baja y resultado registrado. Sin filas de total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Formato de ejemplo con datos ficticios que muestra la estructura esperada. La hoja «Datos» trae los rótulos que la prueba reconoce automáticamente; reemplace las filas por las de su empresa. Si su archivo usa otros nombres de columna, puede cargarlo igual: al procesar podrá mapear a mano dónde está cada dato.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>EJEMPLO · datos ficticios</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Auxiliar de propiedad, planta y equipo por activo al corte</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Una fila por activo o componente: código, descripción, clase, elemento (si es parte), fecha disponible para uso, costo inicial, adiciones, residual, vida útil en meses, método, depreciación acumulada inicial, depreciación del año registrada, deterioro acumulado; si aplica: importe recuperable, valor revaluado, superávit previo, fecha y producto de la baja y resultado registrado. Sin filas de total.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Formato de ejemplo con datos ficticios que muestra la estructura esperada. La hoja «Datos» trae los rótulos que la prueba reconoce automáticamente; reemplace las filas por las de su empresa sin cambiar los encabezados.</t>
-        </is>
-      </c>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>Columna</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>Obligatoria</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>Qué va aquí (ejemplo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>Código del activo</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>Clase</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>Elemento al que pertenece (componente)</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>Opcional</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>Fecha disponible para uso</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>Opcional</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>Costo al inicio del año</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>Adiciones del año</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>Opcional</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>Valor residual</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>Opcional</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>Vida útil (meses)</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>Opcional</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>Método de depreciación</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>Opcional</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>Depreciación acumulada inicial</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>Opcional</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>Depreciación del año registrada</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>Opcional</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>Deterioro acumulado</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>Opcional</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>Importe recuperable</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>Opcional</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>Valor revaluado al corte</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>Opcional</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>Superávit de revaluación previo</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>Opcional</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>Decremento previo del mismo activo reconocido en resultados</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>Opcional</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>Fecha de baja</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>Opcional</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>Producto de la baja</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>Opcional</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>Ganancia (pérdida) registrada en la baja</t>
+        </is>
+      </c>
+      <c r="B30" s="12" t="inlineStr">
+        <is>
+          <t>Opcional</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/frontend/public/ejemplos/ppe_propiedad_planta/RQ-001_activos.xlsx
+++ b/frontend/public/ejemplos/ppe_propiedad_planta/RQ-001_activos.xlsx
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T11"/>
+  <dimension ref="A1:W11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -507,14 +507,17 @@
     <col width="26" customWidth="1" min="10" max="10"/>
     <col width="34" customWidth="1" min="11" max="11"/>
     <col width="34" customWidth="1" min="12" max="12"/>
-    <col width="23" customWidth="1" min="13" max="13"/>
-    <col width="23" customWidth="1" min="14" max="14"/>
-    <col width="28" customWidth="1" min="15" max="15"/>
-    <col width="34" customWidth="1" min="16" max="16"/>
-    <col width="34" customWidth="1" min="17" max="17"/>
-    <col width="17" customWidth="1" min="18" max="18"/>
-    <col width="23" customWidth="1" min="19" max="19"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="27" customWidth="1" min="15" max="15"/>
+    <col width="23" customWidth="1" min="16" max="16"/>
+    <col width="23" customWidth="1" min="17" max="17"/>
+    <col width="28" customWidth="1" min="18" max="18"/>
+    <col width="34" customWidth="1" min="19" max="19"/>
     <col width="34" customWidth="1" min="20" max="20"/>
+    <col width="17" customWidth="1" min="21" max="21"/>
+    <col width="23" customWidth="1" min="22" max="22"/>
+    <col width="34" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -575,45 +578,60 @@
       </c>
       <c r="L1" s="2" t="inlineStr">
         <is>
+          <t>Depreciación acumulada del cliente al corte</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
           <t>Depreciación del año registrada</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>Vida útil (días)</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>% de depreciación anual</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>Deterioro acumulado</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>Importe recuperable</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t>Valor revaluado al corte</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="S1" s="2" t="inlineStr">
         <is>
           <t>Superávit de revaluación previo</t>
         </is>
       </c>
-      <c r="Q1" s="2" t="inlineStr">
+      <c r="T1" s="2" t="inlineStr">
         <is>
           <t>Decremento previo del mismo activo reconocido en resultados</t>
         </is>
       </c>
-      <c r="R1" s="2" t="inlineStr">
+      <c r="U1" s="2" t="inlineStr">
         <is>
           <t>Fecha de baja</t>
         </is>
       </c>
-      <c r="S1" s="2" t="inlineStr">
+      <c r="V1" s="2" t="inlineStr">
         <is>
           <t>Producto de la baja</t>
         </is>
       </c>
-      <c r="T1" s="2" t="inlineStr">
+      <c r="W1" s="2" t="inlineStr">
         <is>
           <t>Ganancia (pérdida) registrada en la baja</t>
         </is>
@@ -667,12 +685,12 @@
           <t>112500</t>
         </is>
       </c>
-      <c r="L2" s="3" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr"/>
+      <c r="M2" s="3" t="inlineStr">
         <is>
           <t>11250</t>
         </is>
       </c>
-      <c r="M2" s="3" t="inlineStr"/>
       <c r="N2" s="3" t="inlineStr"/>
       <c r="O2" s="3" t="inlineStr"/>
       <c r="P2" s="3" t="inlineStr"/>
@@ -680,6 +698,9 @@
       <c r="R2" s="3" t="inlineStr"/>
       <c r="S2" s="3" t="inlineStr"/>
       <c r="T2" s="3" t="inlineStr"/>
+      <c r="U2" s="3" t="inlineStr"/>
+      <c r="V2" s="3" t="inlineStr"/>
+      <c r="W2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -713,23 +734,26 @@
       <c r="I3" s="4" t="inlineStr"/>
       <c r="J3" s="4" t="inlineStr"/>
       <c r="K3" s="4" t="inlineStr"/>
-      <c r="L3" s="4" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr"/>
+      <c r="M3" s="4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M3" s="4" t="inlineStr"/>
       <c r="N3" s="4" t="inlineStr"/>
-      <c r="O3" s="4" t="inlineStr">
-        <is>
-          <t>360000</t>
-        </is>
-      </c>
+      <c r="O3" s="4" t="inlineStr"/>
       <c r="P3" s="4" t="inlineStr"/>
       <c r="Q3" s="4" t="inlineStr"/>
-      <c r="R3" s="4" t="inlineStr"/>
+      <c r="R3" s="4" t="inlineStr">
+        <is>
+          <t>360000</t>
+        </is>
+      </c>
       <c r="S3" s="4" t="inlineStr"/>
       <c r="T3" s="4" t="inlineStr"/>
+      <c r="U3" s="4" t="inlineStr"/>
+      <c r="V3" s="4" t="inlineStr"/>
+      <c r="W3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -763,12 +787,12 @@
       <c r="I4" s="3" t="inlineStr"/>
       <c r="J4" s="3" t="inlineStr"/>
       <c r="K4" s="3" t="inlineStr"/>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr"/>
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr"/>
       <c r="N4" s="3" t="inlineStr"/>
       <c r="O4" s="3" t="inlineStr"/>
       <c r="P4" s="3" t="inlineStr"/>
@@ -776,6 +800,9 @@
       <c r="R4" s="3" t="inlineStr"/>
       <c r="S4" s="3" t="inlineStr"/>
       <c r="T4" s="3" t="inlineStr"/>
+      <c r="U4" s="3" t="inlineStr"/>
+      <c r="V4" s="3" t="inlineStr"/>
+      <c r="W4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -825,12 +852,12 @@
           <t>10800</t>
         </is>
       </c>
-      <c r="L5" s="4" t="inlineStr">
+      <c r="L5" s="4" t="inlineStr"/>
+      <c r="M5" s="4" t="inlineStr">
         <is>
           <t>6000</t>
         </is>
       </c>
-      <c r="M5" s="4" t="inlineStr"/>
       <c r="N5" s="4" t="inlineStr"/>
       <c r="O5" s="4" t="inlineStr"/>
       <c r="P5" s="4" t="inlineStr"/>
@@ -838,6 +865,9 @@
       <c r="R5" s="4" t="inlineStr"/>
       <c r="S5" s="4" t="inlineStr"/>
       <c r="T5" s="4" t="inlineStr"/>
+      <c r="U5" s="4" t="inlineStr"/>
+      <c r="V5" s="4" t="inlineStr"/>
+      <c r="W5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -887,27 +917,30 @@
           <t>21600</t>
         </is>
       </c>
-      <c r="L6" s="3" t="inlineStr">
+      <c r="L6" s="3" t="inlineStr"/>
+      <c r="M6" s="3" t="inlineStr">
         <is>
           <t>2700</t>
         </is>
       </c>
-      <c r="M6" s="3" t="inlineStr"/>
       <c r="N6" s="3" t="inlineStr"/>
       <c r="O6" s="3" t="inlineStr"/>
       <c r="P6" s="3" t="inlineStr"/>
       <c r="Q6" s="3" t="inlineStr"/>
-      <c r="R6" s="3" t="inlineStr">
+      <c r="R6" s="3" t="inlineStr"/>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr"/>
+      <c r="U6" s="3" t="inlineStr">
         <is>
           <t>30/06/2025</t>
         </is>
       </c>
-      <c r="S6" s="3" t="inlineStr">
+      <c r="V6" s="3" t="inlineStr">
         <is>
           <t>9000</t>
         </is>
       </c>
-      <c r="T6" s="3" t="inlineStr">
+      <c r="W6" s="3" t="inlineStr">
         <is>
           <t>1500</t>
         </is>
@@ -957,23 +990,26 @@
           <t>60000</t>
         </is>
       </c>
-      <c r="L7" s="4" t="inlineStr">
+      <c r="L7" s="4" t="inlineStr"/>
+      <c r="M7" s="4" t="inlineStr">
         <is>
           <t>12000</t>
         </is>
       </c>
-      <c r="M7" s="4" t="inlineStr"/>
-      <c r="N7" s="4" t="inlineStr">
-        <is>
-          <t>40000</t>
-        </is>
-      </c>
+      <c r="N7" s="4" t="inlineStr"/>
       <c r="O7" s="4" t="inlineStr"/>
       <c r="P7" s="4" t="inlineStr"/>
-      <c r="Q7" s="4" t="inlineStr"/>
+      <c r="Q7" s="4" t="inlineStr">
+        <is>
+          <t>40000</t>
+        </is>
+      </c>
       <c r="R7" s="4" t="inlineStr"/>
       <c r="S7" s="4" t="inlineStr"/>
       <c r="T7" s="4" t="inlineStr"/>
+      <c r="U7" s="4" t="inlineStr"/>
+      <c r="V7" s="4" t="inlineStr"/>
+      <c r="W7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -1023,12 +1059,12 @@
           <t>30000</t>
         </is>
       </c>
-      <c r="L8" s="3" t="inlineStr">
+      <c r="L8" s="3" t="inlineStr"/>
+      <c r="M8" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="3" t="inlineStr"/>
       <c r="N8" s="3" t="inlineStr"/>
       <c r="O8" s="3" t="inlineStr"/>
       <c r="P8" s="3" t="inlineStr"/>
@@ -1036,6 +1072,9 @@
       <c r="R8" s="3" t="inlineStr"/>
       <c r="S8" s="3" t="inlineStr"/>
       <c r="T8" s="3" t="inlineStr"/>
+      <c r="U8" s="3" t="inlineStr"/>
+      <c r="V8" s="3" t="inlineStr"/>
+      <c r="W8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -1081,12 +1120,12 @@
           <t>5000</t>
         </is>
       </c>
-      <c r="L9" s="4" t="inlineStr">
+      <c r="L9" s="4" t="inlineStr"/>
+      <c r="M9" s="4" t="inlineStr">
         <is>
           <t>4000</t>
         </is>
       </c>
-      <c r="M9" s="4" t="inlineStr"/>
       <c r="N9" s="4" t="inlineStr"/>
       <c r="O9" s="4" t="inlineStr"/>
       <c r="P9" s="4" t="inlineStr"/>
@@ -1094,6 +1133,9 @@
       <c r="R9" s="4" t="inlineStr"/>
       <c r="S9" s="4" t="inlineStr"/>
       <c r="T9" s="4" t="inlineStr"/>
+      <c r="U9" s="4" t="inlineStr"/>
+      <c r="V9" s="4" t="inlineStr"/>
+      <c r="W9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -1127,12 +1169,12 @@
       <c r="I10" s="3" t="inlineStr"/>
       <c r="J10" s="3" t="inlineStr"/>
       <c r="K10" s="3" t="inlineStr"/>
-      <c r="L10" s="3" t="inlineStr">
+      <c r="L10" s="3" t="inlineStr"/>
+      <c r="M10" s="3" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="M10" s="3" t="inlineStr"/>
       <c r="N10" s="3" t="inlineStr"/>
       <c r="O10" s="3" t="inlineStr"/>
       <c r="P10" s="3" t="inlineStr"/>
@@ -1140,6 +1182,9 @@
       <c r="R10" s="3" t="inlineStr"/>
       <c r="S10" s="3" t="inlineStr"/>
       <c r="T10" s="3" t="inlineStr"/>
+      <c r="U10" s="3" t="inlineStr"/>
+      <c r="V10" s="3" t="inlineStr"/>
+      <c r="W10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -1185,12 +1230,12 @@
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr"/>
-      <c r="L11" s="4" t="inlineStr">
+      <c r="L11" s="4" t="inlineStr"/>
+      <c r="M11" s="4" t="inlineStr">
         <is>
           <t>904.11</t>
         </is>
       </c>
-      <c r="M11" s="4" t="inlineStr"/>
       <c r="N11" s="4" t="inlineStr"/>
       <c r="O11" s="4" t="inlineStr"/>
       <c r="P11" s="4" t="inlineStr"/>
@@ -1198,6 +1243,9 @@
       <c r="R11" s="4" t="inlineStr"/>
       <c r="S11" s="4" t="inlineStr"/>
       <c r="T11" s="4" t="inlineStr"/>
+      <c r="U11" s="4" t="inlineStr"/>
+      <c r="V11" s="4" t="inlineStr"/>
+      <c r="W11" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1210,7 +1258,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1416,7 +1464,7 @@
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>Depreciación del año registrada</t>
+          <t>Depreciación acumulada del cliente al corte</t>
         </is>
       </c>
       <c r="B22" s="12" t="inlineStr">
@@ -1429,7 +1477,7 @@
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>Deterioro acumulado</t>
+          <t>Depreciación del año registrada</t>
         </is>
       </c>
       <c r="B23" s="12" t="inlineStr">
@@ -1442,7 +1490,7 @@
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>Importe recuperable</t>
+          <t>Vida útil (días)</t>
         </is>
       </c>
       <c r="B24" s="12" t="inlineStr">
@@ -1455,7 +1503,7 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>Valor revaluado al corte</t>
+          <t>% de depreciación anual</t>
         </is>
       </c>
       <c r="B25" s="12" t="inlineStr">
@@ -1468,7 +1516,7 @@
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>Superávit de revaluación previo</t>
+          <t>Deterioro acumulado</t>
         </is>
       </c>
       <c r="B26" s="12" t="inlineStr">
@@ -1481,7 +1529,7 @@
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>Decremento previo del mismo activo reconocido en resultados</t>
+          <t>Importe recuperable</t>
         </is>
       </c>
       <c r="B27" s="12" t="inlineStr">
@@ -1494,7 +1542,7 @@
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>Fecha de baja</t>
+          <t>Valor revaluado al corte</t>
         </is>
       </c>
       <c r="B28" s="12" t="inlineStr">
@@ -1507,7 +1555,7 @@
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>Producto de la baja</t>
+          <t>Superávit de revaluación previo</t>
         </is>
       </c>
       <c r="B29" s="12" t="inlineStr">
@@ -1520,15 +1568,54 @@
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>
+          <t>Decremento previo del mismo activo reconocido en resultados</t>
+        </is>
+      </c>
+      <c r="B30" s="12" t="inlineStr">
+        <is>
+          <t>Opcional</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>Fecha de baja</t>
+        </is>
+      </c>
+      <c r="B31" s="12" t="inlineStr">
+        <is>
+          <t>Opcional</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>Producto de la baja</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="inlineStr">
+        <is>
+          <t>Opcional</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
           <t>Ganancia (pérdida) registrada en la baja</t>
         </is>
       </c>
-      <c r="B30" s="12" t="inlineStr">
-        <is>
-          <t>Opcional</t>
-        </is>
-      </c>
-      <c r="C30" s="10" t="inlineStr"/>
+      <c r="B33" s="12" t="inlineStr">
+        <is>
+          <t>Opcional</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/frontend/public/ejemplos/ppe_propiedad_planta/RQ-001_activos.xlsx
+++ b/frontend/public/ejemplos/ppe_propiedad_planta/RQ-001_activos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Datos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Instrucciones" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -49,10 +49,6 @@
       <color rgb="00FFFFFF"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="001F6B4C"/>
-    </font>
-    <font>
       <color rgb="006B7280"/>
     </font>
   </fonts>
@@ -65,17 +61,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F6B4C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="006B7280"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E8F1EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F6B4C"/>
       </patternFill>
     </fill>
   </fills>
@@ -105,15 +101,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -121,12 +114,11 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -492,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W11"/>
+  <dimension ref="A1:X11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -504,20 +496,21 @@
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
-    <col width="26" customWidth="1" min="10" max="10"/>
-    <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="31" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
     <col width="34" customWidth="1" min="12" max="12"/>
     <col width="34" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="27" customWidth="1" min="15" max="15"/>
-    <col width="23" customWidth="1" min="16" max="16"/>
+    <col width="34" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="27" customWidth="1" min="16" max="16"/>
     <col width="23" customWidth="1" min="17" max="17"/>
-    <col width="28" customWidth="1" min="18" max="18"/>
-    <col width="34" customWidth="1" min="19" max="19"/>
+    <col width="23" customWidth="1" min="18" max="18"/>
+    <col width="28" customWidth="1" min="19" max="19"/>
     <col width="34" customWidth="1" min="20" max="20"/>
-    <col width="17" customWidth="1" min="21" max="21"/>
-    <col width="23" customWidth="1" min="22" max="22"/>
-    <col width="34" customWidth="1" min="23" max="23"/>
+    <col width="34" customWidth="1" min="21" max="21"/>
+    <col width="17" customWidth="1" min="22" max="22"/>
+    <col width="23" customWidth="1" min="23" max="23"/>
+    <col width="34" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -536,12 +529,12 @@
           <t>Clase</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Elemento al que pertenece (componente)</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Fecha disponible para uso</t>
         </is>
@@ -551,701 +544,716 @@
           <t>Costo al inicio del año</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Adiciones del año</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Valor residual</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Vida útil (meses)</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Vida útil tributaria (años)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Método de depreciación</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Depreciación acumulada inicial</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Depreciación acumulada del cliente al corte</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Depreciación del año registrada</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Vida útil (días)</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>% de depreciación anual</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Deterioro acumulado</t>
         </is>
       </c>
-      <c r="Q1" s="2" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Importe recuperable</t>
         </is>
       </c>
-      <c r="R1" s="2" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Valor revaluado al corte</t>
         </is>
       </c>
-      <c r="S1" s="2" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Superávit de revaluación previo</t>
         </is>
       </c>
-      <c r="T1" s="2" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Decremento previo del mismo activo reconocido en resultados</t>
         </is>
       </c>
-      <c r="U1" s="2" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Fecha de baja</t>
         </is>
       </c>
-      <c r="V1" s="2" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Producto de la baja</t>
         </is>
       </c>
-      <c r="W1" s="2" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Ganancia (pérdida) registrada en la baja</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>EDIF-01</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Edificio administrativo</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Edificios</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr"/>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>01/01/2015</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>500000</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr"/>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>50000</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>480</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>Lineal</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>112500</t>
         </is>
       </c>
-      <c r="L2" s="3" t="inlineStr"/>
-      <c r="M2" s="3" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>11250</t>
         </is>
       </c>
-      <c r="N2" s="3" t="inlineStr"/>
-      <c r="O2" s="3" t="inlineStr"/>
-      <c r="P2" s="3" t="inlineStr"/>
-      <c r="Q2" s="3" t="inlineStr"/>
-      <c r="R2" s="3" t="inlineStr"/>
-      <c r="S2" s="3" t="inlineStr"/>
-      <c r="T2" s="3" t="inlineStr"/>
-      <c r="U2" s="3" t="inlineStr"/>
-      <c r="V2" s="3" t="inlineStr"/>
-      <c r="W2" s="3" t="inlineStr"/>
+      <c r="O2" s="2" t="inlineStr"/>
+      <c r="P2" s="2" t="inlineStr"/>
+      <c r="Q2" s="2" t="inlineStr"/>
+      <c r="R2" s="2" t="inlineStr"/>
+      <c r="S2" s="2" t="inlineStr"/>
+      <c r="T2" s="2" t="inlineStr"/>
+      <c r="U2" s="2" t="inlineStr"/>
+      <c r="V2" s="2" t="inlineStr"/>
+      <c r="W2" s="2" t="inlineStr"/>
+      <c r="X2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>TERR-01</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Terreno planta</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Terrenos</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr"/>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr"/>
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>01/01/2015</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>300000</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr"/>
-      <c r="H3" s="4" t="inlineStr"/>
-      <c r="I3" s="4" t="inlineStr"/>
-      <c r="J3" s="4" t="inlineStr"/>
-      <c r="K3" s="4" t="inlineStr"/>
-      <c r="L3" s="4" t="inlineStr"/>
-      <c r="M3" s="4" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr"/>
+      <c r="J3" s="3" t="inlineStr"/>
+      <c r="K3" s="3" t="inlineStr"/>
+      <c r="L3" s="3" t="inlineStr"/>
+      <c r="M3" s="3" t="inlineStr"/>
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N3" s="4" t="inlineStr"/>
-      <c r="O3" s="4" t="inlineStr"/>
-      <c r="P3" s="4" t="inlineStr"/>
-      <c r="Q3" s="4" t="inlineStr"/>
-      <c r="R3" s="4" t="inlineStr">
+      <c r="O3" s="3" t="inlineStr"/>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr"/>
+      <c r="S3" s="3" t="inlineStr">
         <is>
           <t>360000</t>
         </is>
       </c>
-      <c r="S3" s="4" t="inlineStr"/>
-      <c r="T3" s="4" t="inlineStr"/>
-      <c r="U3" s="4" t="inlineStr"/>
-      <c r="V3" s="4" t="inlineStr"/>
-      <c r="W3" s="4" t="inlineStr"/>
+      <c r="T3" s="3" t="inlineStr"/>
+      <c r="U3" s="3" t="inlineStr"/>
+      <c r="V3" s="3" t="inlineStr"/>
+      <c r="W3" s="3" t="inlineStr"/>
+      <c r="X3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>TERR-02</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Terreno bodega</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Terrenos</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr"/>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>01/05/2018</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>80000</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr"/>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
-      <c r="J4" s="3" t="inlineStr"/>
-      <c r="K4" s="3" t="inlineStr"/>
-      <c r="L4" s="3" t="inlineStr"/>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr"/>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr"/>
-      <c r="O4" s="3" t="inlineStr"/>
-      <c r="P4" s="3" t="inlineStr"/>
-      <c r="Q4" s="3" t="inlineStr"/>
-      <c r="R4" s="3" t="inlineStr"/>
-      <c r="S4" s="3" t="inlineStr"/>
-      <c r="T4" s="3" t="inlineStr"/>
-      <c r="U4" s="3" t="inlineStr"/>
-      <c r="V4" s="3" t="inlineStr"/>
-      <c r="W4" s="3" t="inlineStr"/>
+      <c r="O4" s="2" t="inlineStr"/>
+      <c r="P4" s="2" t="inlineStr"/>
+      <c r="Q4" s="2" t="inlineStr"/>
+      <c r="R4" s="2" t="inlineStr"/>
+      <c r="S4" s="2" t="inlineStr"/>
+      <c r="T4" s="2" t="inlineStr"/>
+      <c r="U4" s="2" t="inlineStr"/>
+      <c r="V4" s="2" t="inlineStr"/>
+      <c r="W4" s="2" t="inlineStr"/>
+      <c r="X4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>VEH-01</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Camioneta 4x4</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Vehículos</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr"/>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>01/07/2023</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>40000</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr"/>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>4000</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr"/>
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>Lineal</t>
         </is>
       </c>
-      <c r="K5" s="4" t="inlineStr">
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>10800</t>
         </is>
       </c>
-      <c r="L5" s="4" t="inlineStr"/>
-      <c r="M5" s="4" t="inlineStr">
+      <c r="M5" s="3" t="inlineStr"/>
+      <c r="N5" s="3" t="inlineStr">
         <is>
           <t>6000</t>
         </is>
       </c>
-      <c r="N5" s="4" t="inlineStr"/>
-      <c r="O5" s="4" t="inlineStr"/>
-      <c r="P5" s="4" t="inlineStr"/>
-      <c r="Q5" s="4" t="inlineStr"/>
-      <c r="R5" s="4" t="inlineStr"/>
-      <c r="S5" s="4" t="inlineStr"/>
-      <c r="T5" s="4" t="inlineStr"/>
-      <c r="U5" s="4" t="inlineStr"/>
-      <c r="V5" s="4" t="inlineStr"/>
-      <c r="W5" s="4" t="inlineStr"/>
+      <c r="O5" s="3" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr"/>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr"/>
+      <c r="V5" s="3" t="inlineStr"/>
+      <c r="W5" s="3" t="inlineStr"/>
+      <c r="X5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>VEH-02</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Camión de reparto</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Vehículos</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr"/>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>01/01/2021</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>30000</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>Lineal</t>
         </is>
       </c>
-      <c r="K6" s="3" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>21600</t>
         </is>
       </c>
-      <c r="L6" s="3" t="inlineStr"/>
-      <c r="M6" s="3" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>2700</t>
         </is>
       </c>
-      <c r="N6" s="3" t="inlineStr"/>
-      <c r="O6" s="3" t="inlineStr"/>
-      <c r="P6" s="3" t="inlineStr"/>
-      <c r="Q6" s="3" t="inlineStr"/>
-      <c r="R6" s="3" t="inlineStr"/>
-      <c r="S6" s="3" t="inlineStr"/>
-      <c r="T6" s="3" t="inlineStr"/>
-      <c r="U6" s="3" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr"/>
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr"/>
+      <c r="S6" s="2" t="inlineStr"/>
+      <c r="T6" s="2" t="inlineStr"/>
+      <c r="U6" s="2" t="inlineStr"/>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>30/06/2025</t>
         </is>
       </c>
-      <c r="V6" s="3" t="inlineStr">
+      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>9000</t>
         </is>
       </c>
-      <c r="W6" s="3" t="inlineStr">
+      <c r="X6" s="2" t="inlineStr">
         <is>
           <t>1500</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>MAQ-01</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Línea de envasado</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>Maquinaria</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr"/>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>01/01/2020</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>120000</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr"/>
-      <c r="H7" s="4" t="inlineStr"/>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>120</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr"/>
+      <c r="K7" s="3" t="inlineStr">
         <is>
           <t>Lineal</t>
         </is>
       </c>
-      <c r="K7" s="4" t="inlineStr">
+      <c r="L7" s="3" t="inlineStr">
         <is>
           <t>60000</t>
         </is>
       </c>
-      <c r="L7" s="4" t="inlineStr"/>
-      <c r="M7" s="4" t="inlineStr">
+      <c r="M7" s="3" t="inlineStr"/>
+      <c r="N7" s="3" t="inlineStr">
         <is>
           <t>12000</t>
         </is>
       </c>
-      <c r="N7" s="4" t="inlineStr"/>
-      <c r="O7" s="4" t="inlineStr"/>
-      <c r="P7" s="4" t="inlineStr"/>
-      <c r="Q7" s="4" t="inlineStr">
+      <c r="O7" s="3" t="inlineStr"/>
+      <c r="P7" s="3" t="inlineStr"/>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr">
         <is>
           <t>40000</t>
         </is>
       </c>
-      <c r="R7" s="4" t="inlineStr"/>
-      <c r="S7" s="4" t="inlineStr"/>
-      <c r="T7" s="4" t="inlineStr"/>
-      <c r="U7" s="4" t="inlineStr"/>
-      <c r="V7" s="4" t="inlineStr"/>
-      <c r="W7" s="4" t="inlineStr"/>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr"/>
+      <c r="U7" s="3" t="inlineStr"/>
+      <c r="V7" s="3" t="inlineStr"/>
+      <c r="W7" s="3" t="inlineStr"/>
+      <c r="X7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>MAQ-01-M</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Motor de la línea de envasado</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Maquinaria</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>MAQ-01</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>01/01/2020</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>30000</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>Lineal</t>
         </is>
       </c>
-      <c r="K8" s="3" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>30000</t>
         </is>
       </c>
-      <c r="L8" s="3" t="inlineStr"/>
-      <c r="M8" s="3" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N8" s="3" t="inlineStr"/>
-      <c r="O8" s="3" t="inlineStr"/>
-      <c r="P8" s="3" t="inlineStr"/>
-      <c r="Q8" s="3" t="inlineStr"/>
-      <c r="R8" s="3" t="inlineStr"/>
-      <c r="S8" s="3" t="inlineStr"/>
-      <c r="T8" s="3" t="inlineStr"/>
-      <c r="U8" s="3" t="inlineStr"/>
-      <c r="V8" s="3" t="inlineStr"/>
-      <c r="W8" s="3" t="inlineStr"/>
+      <c r="O8" s="2" t="inlineStr"/>
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="R8" s="2" t="inlineStr"/>
+      <c r="S8" s="2" t="inlineStr"/>
+      <c r="T8" s="2" t="inlineStr"/>
+      <c r="U8" s="2" t="inlineStr"/>
+      <c r="V8" s="2" t="inlineStr"/>
+      <c r="W8" s="2" t="inlineStr"/>
+      <c r="X8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>EQC-01</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Servidores</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Equipo de cómputo</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr"/>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr"/>
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>01/01/2024</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>15000</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr"/>
-      <c r="H9" s="4" t="inlineStr"/>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="J9" s="3" t="inlineStr"/>
+      <c r="K9" s="3" t="inlineStr">
         <is>
           <t>Unidades producidas</t>
         </is>
       </c>
-      <c r="K9" s="4" t="inlineStr">
+      <c r="L9" s="3" t="inlineStr">
         <is>
           <t>5000</t>
         </is>
       </c>
-      <c r="L9" s="4" t="inlineStr"/>
-      <c r="M9" s="4" t="inlineStr">
+      <c r="M9" s="3" t="inlineStr"/>
+      <c r="N9" s="3" t="inlineStr">
         <is>
           <t>4000</t>
         </is>
       </c>
-      <c r="N9" s="4" t="inlineStr"/>
-      <c r="O9" s="4" t="inlineStr"/>
-      <c r="P9" s="4" t="inlineStr"/>
-      <c r="Q9" s="4" t="inlineStr"/>
-      <c r="R9" s="4" t="inlineStr"/>
-      <c r="S9" s="4" t="inlineStr"/>
-      <c r="T9" s="4" t="inlineStr"/>
-      <c r="U9" s="4" t="inlineStr"/>
-      <c r="V9" s="4" t="inlineStr"/>
-      <c r="W9" s="4" t="inlineStr"/>
+      <c r="O9" s="3" t="inlineStr"/>
+      <c r="P9" s="3" t="inlineStr"/>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr"/>
+      <c r="S9" s="3" t="inlineStr"/>
+      <c r="T9" s="3" t="inlineStr"/>
+      <c r="U9" s="3" t="inlineStr"/>
+      <c r="V9" s="3" t="inlineStr"/>
+      <c r="W9" s="3" t="inlineStr"/>
+      <c r="X9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>OBRA-01</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Nave industrial en construcción</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Construcciones en curso</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr"/>
-      <c r="E10" s="3" t="inlineStr"/>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr"/>
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr"/>
-      <c r="I10" s="3" t="inlineStr"/>
-      <c r="J10" s="3" t="inlineStr"/>
-      <c r="K10" s="3" t="inlineStr"/>
-      <c r="L10" s="3" t="inlineStr"/>
-      <c r="M10" s="3" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="N10" s="3" t="inlineStr"/>
-      <c r="O10" s="3" t="inlineStr"/>
-      <c r="P10" s="3" t="inlineStr"/>
-      <c r="Q10" s="3" t="inlineStr"/>
-      <c r="R10" s="3" t="inlineStr"/>
-      <c r="S10" s="3" t="inlineStr"/>
-      <c r="T10" s="3" t="inlineStr"/>
-      <c r="U10" s="3" t="inlineStr"/>
-      <c r="V10" s="3" t="inlineStr"/>
-      <c r="W10" s="3" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr"/>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr"/>
+      <c r="V10" s="2" t="inlineStr"/>
+      <c r="W10" s="2" t="inlineStr"/>
+      <c r="X10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>MOB-01</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Mobiliario de oficinas</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>Muebles y enseres</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr"/>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr"/>
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>01/04/2025</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>12000</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr"/>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr"/>
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t>120</t>
         </is>
       </c>
-      <c r="J11" s="4" t="inlineStr">
+      <c r="J11" s="3" t="inlineStr"/>
+      <c r="K11" s="3" t="inlineStr">
         <is>
           <t>Lineal</t>
         </is>
       </c>
-      <c r="K11" s="4" t="inlineStr"/>
-      <c r="L11" s="4" t="inlineStr"/>
-      <c r="M11" s="4" t="inlineStr">
+      <c r="L11" s="3" t="inlineStr"/>
+      <c r="M11" s="3" t="inlineStr"/>
+      <c r="N11" s="3" t="inlineStr">
         <is>
           <t>904.11</t>
         </is>
       </c>
-      <c r="N11" s="4" t="inlineStr"/>
-      <c r="O11" s="4" t="inlineStr"/>
-      <c r="P11" s="4" t="inlineStr"/>
-      <c r="Q11" s="4" t="inlineStr"/>
-      <c r="R11" s="4" t="inlineStr"/>
-      <c r="S11" s="4" t="inlineStr"/>
-      <c r="T11" s="4" t="inlineStr"/>
-      <c r="U11" s="4" t="inlineStr"/>
-      <c r="V11" s="4" t="inlineStr"/>
-      <c r="W11" s="4" t="inlineStr"/>
+      <c r="O11" s="3" t="inlineStr"/>
+      <c r="P11" s="3" t="inlineStr"/>
+      <c r="Q11" s="3" t="inlineStr"/>
+      <c r="R11" s="3" t="inlineStr"/>
+      <c r="S11" s="3" t="inlineStr"/>
+      <c r="T11" s="3" t="inlineStr"/>
+      <c r="U11" s="3" t="inlineStr"/>
+      <c r="V11" s="3" t="inlineStr"/>
+      <c r="W11" s="3" t="inlineStr"/>
+      <c r="X11" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1258,7 +1266,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1267,355 +1275,368 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>AuditConsulting Auditores Cía. Ltda.</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>Auxiliar de propiedad, planta y equipo por activo al corte</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>Una fila por activo o componente: código, descripción, clase, elemento (si es parte), fecha disponible para uso, costo inicial, adiciones, residual, vida útil en meses, método, depreciación acumulada inicial, depreciación del año registrada, deterioro acumulado; si aplica: importe recuperable, valor revaluado, superávit previo, fecha y producto de la baja y resultado registrado. Sin filas de total.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>Formato de ejemplo con datos ficticios que muestra la estructura esperada. La hoja «Datos» trae los rótulos que la prueba reconoce automáticamente; reemplace las filas por las de su empresa. Si su archivo usa otros nombres de columna, puede cargarlo igual: al procesar podrá mapear a mano dónde está cada dato.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>EJEMPLO · datos ficticios</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>Columna</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>Obligatoria</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>Qué va aquí (ejemplo)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>Código del activo</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="inlineStr"/>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Opcional</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>Descripción</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="inlineStr"/>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>Opcional</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>Clase</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C13" s="10" t="inlineStr"/>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>Opcional</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>Elemento al que pertenece (componente)</t>
         </is>
       </c>
-      <c r="B14" s="12" t="inlineStr">
-        <is>
-          <t>Opcional</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr"/>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>Opcional</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>Fecha disponible para uso</t>
         </is>
       </c>
-      <c r="B15" s="12" t="inlineStr">
-        <is>
-          <t>Opcional</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="inlineStr"/>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>Opcional</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>Costo al inicio del año</t>
         </is>
       </c>
-      <c r="B16" s="11" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C16" s="10" t="inlineStr"/>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>Opcional</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>Adiciones del año</t>
         </is>
       </c>
-      <c r="B17" s="12" t="inlineStr">
-        <is>
-          <t>Opcional</t>
-        </is>
-      </c>
-      <c r="C17" s="10" t="inlineStr"/>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>Opcional</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>Valor residual</t>
         </is>
       </c>
-      <c r="B18" s="12" t="inlineStr">
-        <is>
-          <t>Opcional</t>
-        </is>
-      </c>
-      <c r="C18" s="10" t="inlineStr"/>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>Opcional</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>Vida útil (meses)</t>
         </is>
       </c>
-      <c r="B19" s="12" t="inlineStr">
-        <is>
-          <t>Opcional</t>
-        </is>
-      </c>
-      <c r="C19" s="10" t="inlineStr"/>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>Opcional</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>Vida útil tributaria (años)</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>Opcional</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>Método de depreciación</t>
         </is>
       </c>
-      <c r="B20" s="12" t="inlineStr">
-        <is>
-          <t>Opcional</t>
-        </is>
-      </c>
-      <c r="C20" s="10" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="10" t="inlineStr">
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>Opcional</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>Depreciación acumulada inicial</t>
         </is>
       </c>
-      <c r="B21" s="12" t="inlineStr">
-        <is>
-          <t>Opcional</t>
-        </is>
-      </c>
-      <c r="C21" s="10" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="10" t="inlineStr">
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>Opcional</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>Depreciación acumulada del cliente al corte</t>
         </is>
       </c>
-      <c r="B22" s="12" t="inlineStr">
-        <is>
-          <t>Opcional</t>
-        </is>
-      </c>
-      <c r="C22" s="10" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="10" t="inlineStr">
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>Opcional</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>Depreciación del año registrada</t>
         </is>
       </c>
-      <c r="B23" s="12" t="inlineStr">
-        <is>
-          <t>Opcional</t>
-        </is>
-      </c>
-      <c r="C23" s="10" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="10" t="inlineStr">
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>Opcional</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>Vida útil (días)</t>
         </is>
       </c>
-      <c r="B24" s="12" t="inlineStr">
-        <is>
-          <t>Opcional</t>
-        </is>
-      </c>
-      <c r="C24" s="10" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="10" t="inlineStr">
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>Opcional</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>% de depreciación anual</t>
         </is>
       </c>
-      <c r="B25" s="12" t="inlineStr">
-        <is>
-          <t>Opcional</t>
-        </is>
-      </c>
-      <c r="C25" s="10" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="10" t="inlineStr">
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>Opcional</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t>Deterioro acumulado</t>
         </is>
       </c>
-      <c r="B26" s="12" t="inlineStr">
-        <is>
-          <t>Opcional</t>
-        </is>
-      </c>
-      <c r="C26" s="10" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="10" t="inlineStr">
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>Opcional</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>Importe recuperable</t>
         </is>
       </c>
-      <c r="B27" s="12" t="inlineStr">
-        <is>
-          <t>Opcional</t>
-        </is>
-      </c>
-      <c r="C27" s="10" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="10" t="inlineStr">
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>Opcional</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t>Valor revaluado al corte</t>
         </is>
       </c>
-      <c r="B28" s="12" t="inlineStr">
-        <is>
-          <t>Opcional</t>
-        </is>
-      </c>
-      <c r="C28" s="10" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="10" t="inlineStr">
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>Opcional</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>Superávit de revaluación previo</t>
         </is>
       </c>
-      <c r="B29" s="12" t="inlineStr">
-        <is>
-          <t>Opcional</t>
-        </is>
-      </c>
-      <c r="C29" s="10" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="10" t="inlineStr">
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>Opcional</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
         <is>
           <t>Decremento previo del mismo activo reconocido en resultados</t>
         </is>
       </c>
-      <c r="B30" s="12" t="inlineStr">
-        <is>
-          <t>Opcional</t>
-        </is>
-      </c>
-      <c r="C30" s="10" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="10" t="inlineStr">
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>Opcional</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
         <is>
           <t>Fecha de baja</t>
         </is>
       </c>
-      <c r="B31" s="12" t="inlineStr">
-        <is>
-          <t>Opcional</t>
-        </is>
-      </c>
-      <c r="C31" s="10" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="10" t="inlineStr">
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>Opcional</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
         <is>
           <t>Producto de la baja</t>
         </is>
       </c>
-      <c r="B32" s="12" t="inlineStr">
-        <is>
-          <t>Opcional</t>
-        </is>
-      </c>
-      <c r="C32" s="10" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="10" t="inlineStr">
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>Opcional</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
         <is>
           <t>Ganancia (pérdida) registrada en la baja</t>
         </is>
       </c>
-      <c r="B33" s="12" t="inlineStr">
-        <is>
-          <t>Opcional</t>
-        </is>
-      </c>
-      <c r="C33" s="10" t="inlineStr"/>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>Opcional</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
